--- a/data/unitTests/excelTest/Feriekasse.xlsx
+++ b/data/unitTests/excelTest/Feriekasse.xlsx
@@ -29,10 +29,10 @@
       <color rgb="00ff9933"/>
     </font>
     <font>
-      <color rgb="000000ff"/>
+      <color rgb="00ff0000"/>
     </font>
     <font>
-      <color rgb="00000000"/>
+      <color rgb="00ff00ff"/>
     </font>
   </fonts>
   <fills count="2">
@@ -475,7 +475,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>league1</t>
+          <t>eng.1</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>league2</t>
+          <t>den.1</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>league3</t>
+          <t>esp.1</t>
         </is>
       </c>
     </row>
